--- a/docs/olife-geo/장소_질문_전체.xlsx
+++ b/docs/olife-geo/장소_질문_전체.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3034" uniqueCount="814">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3028" uniqueCount="812">
   <si>
     <t>프로그램</t>
   </si>
@@ -2423,12 +2423,6 @@
   </si>
   <si>
     <t>세부 장소 (답)</t>
-  </si>
-  <si>
-    <t>2391</t>
-  </si>
-  <si>
-    <t>한번쯤은,하염없이</t>
   </si>
   <si>
     <t>1642</t>
@@ -15279,7 +15273,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -15322,7 +15316,7 @@
         <v>12</v>
       </c>
       <c r="B2">
-        <v>2391</v>
+        <v>1642</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
@@ -15334,7 +15328,7 @@
         <v>804</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G2" t="s">
         <v>15</v>
@@ -15348,7 +15342,7 @@
         <v>12</v>
       </c>
       <c r="B3">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
@@ -15357,41 +15351,15 @@
         <v>805</v>
       </c>
       <c r="E3" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3" t="s">
         <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4">
-        <v>1641</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>807</v>
-      </c>
-      <c r="E4" t="s">
-        <v>806</v>
-      </c>
-      <c r="F4">
-        <v>5</v>
-      </c>
-      <c r="G4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" t="s">
         <v>15</v>
       </c>
     </row>
@@ -15412,7 +15380,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -15422,27 +15390,27 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
     </row>
   </sheetData>

--- a/docs/olife-geo/장소_질문_전체.xlsx
+++ b/docs/olife-geo/장소_질문_전체.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3028" uniqueCount="812">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3016" uniqueCount="809">
   <si>
     <t>프로그램</t>
   </si>
@@ -2423,15 +2423,6 @@
   </si>
   <si>
     <t>세부 장소 (답)</t>
-  </si>
-  <si>
-    <t>1642</t>
-  </si>
-  <si>
-    <t>신비와모험의땅,아라비아반도</t>
-  </si>
-  <si>
-    <t>1641</t>
   </si>
   <si>
     <t>장소·나라 확인 질문 — 이 파일 하나에 답해 주시면 한 번에 반영합니다.</t>
@@ -15273,7 +15264,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -15309,58 +15300,6 @@
       </c>
       <c r="H1" s="2" t="s">
         <v>802</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2">
-        <v>1642</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>803</v>
-      </c>
-      <c r="E2" t="s">
-        <v>804</v>
-      </c>
-      <c r="F2">
-        <v>4</v>
-      </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3">
-        <v>1641</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>805</v>
-      </c>
-      <c r="E3" t="s">
-        <v>804</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="G3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -15380,7 +15319,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -15390,27 +15329,27 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
     </row>
   </sheetData>
